--- a/artfynd/A 29272-2024 artfynd.xlsx
+++ b/artfynd/A 29272-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121697871</v>
+        <v>121696849</v>
       </c>
       <c r="B2" t="n">
-        <v>57373</v>
+        <v>79697</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -748,19 +748,9 @@
           <t>2024-12-20</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>11:50</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-12-20</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>11:50</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121696849</v>
+        <v>121697871</v>
       </c>
       <c r="B3" t="n">
-        <v>79697</v>
+        <v>57373</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -860,9 +850,19 @@
           <t>2024-12-20</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-12-20</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 29272-2024 artfynd.xlsx
+++ b/artfynd/A 29272-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121696849</v>
+        <v>121696840</v>
       </c>
       <c r="B2" t="n">
-        <v>79697</v>
+        <v>78616</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121697871</v>
+        <v>121696849</v>
       </c>
       <c r="B3" t="n">
-        <v>57373</v>
+        <v>79697</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -850,19 +850,9 @@
           <t>2024-12-20</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>11:50</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-12-20</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>11:50</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -991,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121696840</v>
+        <v>121697871</v>
       </c>
       <c r="B5" t="n">
-        <v>78616</v>
+        <v>57373</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1064,9 +1054,19 @@
           <t>2024-12-20</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-12-20</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 29272-2024 artfynd.xlsx
+++ b/artfynd/A 29272-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121696840</v>
+        <v>121697871</v>
       </c>
       <c r="B2" t="n">
-        <v>78616</v>
+        <v>57373</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -748,9 +748,19 @@
           <t>2024-12-20</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-12-20</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121696849</v>
+        <v>121696844</v>
       </c>
       <c r="B3" t="n">
-        <v>79697</v>
+        <v>55959</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>206004</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -879,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121696844</v>
+        <v>121696849</v>
       </c>
       <c r="B4" t="n">
-        <v>55959</v>
+        <v>79697</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>206004</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -981,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121697871</v>
+        <v>121696840</v>
       </c>
       <c r="B5" t="n">
-        <v>57373</v>
+        <v>78616</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1054,19 +1064,9 @@
           <t>2024-12-20</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>11:50</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-12-20</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>11:50</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 29272-2024 artfynd.xlsx
+++ b/artfynd/A 29272-2024 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121696844</v>
+        <v>121696849</v>
       </c>
       <c r="B3" t="n">
-        <v>55959</v>
+        <v>79697</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>206004</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121696849</v>
+        <v>121696840</v>
       </c>
       <c r="B4" t="n">
-        <v>79697</v>
+        <v>78616</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -991,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121696840</v>
+        <v>121696844</v>
       </c>
       <c r="B5" t="n">
-        <v>78616</v>
+        <v>55959</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>206004</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>

--- a/artfynd/A 29272-2024 artfynd.xlsx
+++ b/artfynd/A 29272-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121697871</v>
+        <v>121696844</v>
       </c>
       <c r="B2" t="n">
-        <v>57373</v>
+        <v>55959</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>206004</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -748,19 +748,9 @@
           <t>2024-12-20</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>11:50</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-12-20</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>11:50</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -889,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121696840</v>
+        <v>121697871</v>
       </c>
       <c r="B4" t="n">
-        <v>78616</v>
+        <v>57373</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -962,9 +952,19 @@
           <t>2024-12-20</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-12-20</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121696844</v>
+        <v>121696840</v>
       </c>
       <c r="B5" t="n">
-        <v>55959</v>
+        <v>78616</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>206004</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>

--- a/artfynd/A 29272-2024 artfynd.xlsx
+++ b/artfynd/A 29272-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121696844</v>
+        <v>121696849</v>
       </c>
       <c r="B2" t="n">
-        <v>55959</v>
+        <v>79697</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>206004</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121696849</v>
+        <v>121696844</v>
       </c>
       <c r="B3" t="n">
-        <v>79697</v>
+        <v>55959</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>206004</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121697871</v>
+        <v>121696840</v>
       </c>
       <c r="B4" t="n">
-        <v>57373</v>
+        <v>78616</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -952,19 +952,9 @@
           <t>2024-12-20</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>11:50</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-12-20</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>11:50</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121696840</v>
+        <v>121697871</v>
       </c>
       <c r="B5" t="n">
-        <v>78616</v>
+        <v>57373</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1064,9 +1054,19 @@
           <t>2024-12-20</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-12-20</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 29272-2024 artfynd.xlsx
+++ b/artfynd/A 29272-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>121696849</v>
       </c>
       <c r="B2" t="n">
-        <v>79697</v>
+        <v>79710</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>121696844</v>
       </c>
       <c r="B3" t="n">
-        <v>55959</v>
+        <v>55967</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121696840</v>
+        <v>121697871</v>
       </c>
       <c r="B4" t="n">
-        <v>78616</v>
+        <v>57381</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -952,9 +952,19 @@
           <t>2024-12-20</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-12-20</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121697871</v>
+        <v>121696840</v>
       </c>
       <c r="B5" t="n">
-        <v>57373</v>
+        <v>78629</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1054,19 +1064,9 @@
           <t>2024-12-20</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>11:50</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-12-20</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>11:50</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1090,6 +1090,618 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>122040097</v>
+      </c>
+      <c r="B6" t="n">
+        <v>97085</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Stortjärndalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>564799</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6991861</v>
+      </c>
+      <c r="S6" t="n">
+        <v>50</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>122040069</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79710</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Stortjärndalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>564823</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6991869</v>
+      </c>
+      <c r="S7" t="n">
+        <v>50</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>122040064</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79710</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Stortjärndalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>564903</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6991894</v>
+      </c>
+      <c r="S8" t="n">
+        <v>50</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>122040073</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79710</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Stortjärndalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>564799</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6991861</v>
+      </c>
+      <c r="S9" t="n">
+        <v>50</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>122040079</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79710</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Stortjärndalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>564859</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6991885</v>
+      </c>
+      <c r="S10" t="n">
+        <v>50</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>122040082</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79710</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Stortjärndalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>564751</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6991849</v>
+      </c>
+      <c r="S11" t="n">
+        <v>50</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 29272-2024 artfynd.xlsx
+++ b/artfynd/A 29272-2024 artfynd.xlsx
@@ -1093,7 +1093,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122040069</v>
+        <v>122040073</v>
       </c>
       <c r="B6" t="n">
         <v>79726</v>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>564823</v>
+        <v>564799</v>
       </c>
       <c r="R6" t="n">
-        <v>6991869</v>
+        <v>6991861</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1195,7 +1195,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122040079</v>
+        <v>122040069</v>
       </c>
       <c r="B7" t="n">
         <v>79726</v>
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>564859</v>
+        <v>564823</v>
       </c>
       <c r="R7" t="n">
-        <v>6991885</v>
+        <v>6991869</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1297,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122040097</v>
+        <v>122040064</v>
       </c>
       <c r="B8" t="n">
-        <v>97129</v>
+        <v>79726</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1309,25 +1309,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1337,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>564799</v>
+        <v>564903</v>
       </c>
       <c r="R8" t="n">
-        <v>6991861</v>
+        <v>6991894</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1399,7 +1399,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122040073</v>
+        <v>122040079</v>
       </c>
       <c r="B9" t="n">
         <v>79726</v>
@@ -1439,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>564799</v>
+        <v>564859</v>
       </c>
       <c r="R9" t="n">
-        <v>6991861</v>
+        <v>6991885</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1501,7 +1501,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122040064</v>
+        <v>122040082</v>
       </c>
       <c r="B10" t="n">
         <v>79726</v>
@@ -1541,10 +1541,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>564903</v>
+        <v>564751</v>
       </c>
       <c r="R10" t="n">
-        <v>6991894</v>
+        <v>6991849</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1603,10 +1603,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122040082</v>
+        <v>122040097</v>
       </c>
       <c r="B11" t="n">
-        <v>79726</v>
+        <v>97129</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1615,25 +1615,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1643,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>564751</v>
+        <v>564799</v>
       </c>
       <c r="R11" t="n">
-        <v>6991849</v>
+        <v>6991861</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>

--- a/artfynd/A 29272-2024 artfynd.xlsx
+++ b/artfynd/A 29272-2024 artfynd.xlsx
@@ -1093,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122040073</v>
+        <v>122040064</v>
       </c>
       <c r="B6" t="n">
-        <v>79726</v>
+        <v>79727</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>564799</v>
+        <v>564903</v>
       </c>
       <c r="R6" t="n">
-        <v>6991861</v>
+        <v>6991894</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1195,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122040069</v>
+        <v>122040073</v>
       </c>
       <c r="B7" t="n">
-        <v>79726</v>
+        <v>79727</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>564823</v>
+        <v>564799</v>
       </c>
       <c r="R7" t="n">
-        <v>6991869</v>
+        <v>6991861</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1297,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122040064</v>
+        <v>122040069</v>
       </c>
       <c r="B8" t="n">
-        <v>79726</v>
+        <v>79727</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1337,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>564903</v>
+        <v>564823</v>
       </c>
       <c r="R8" t="n">
-        <v>6991894</v>
+        <v>6991869</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1399,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122040079</v>
+        <v>122040082</v>
       </c>
       <c r="B9" t="n">
-        <v>79726</v>
+        <v>79727</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1439,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>564859</v>
+        <v>564751</v>
       </c>
       <c r="R9" t="n">
-        <v>6991885</v>
+        <v>6991849</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1501,10 +1501,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122040082</v>
+        <v>122040097</v>
       </c>
       <c r="B10" t="n">
-        <v>79726</v>
+        <v>97139</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1513,25 +1513,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1541,10 +1541,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>564751</v>
+        <v>564799</v>
       </c>
       <c r="R10" t="n">
-        <v>6991849</v>
+        <v>6991861</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1603,10 +1603,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122040097</v>
+        <v>122040079</v>
       </c>
       <c r="B11" t="n">
-        <v>97129</v>
+        <v>79727</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1615,25 +1615,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1643,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>564799</v>
+        <v>564859</v>
       </c>
       <c r="R11" t="n">
-        <v>6991861</v>
+        <v>6991885</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>

--- a/artfynd/A 29272-2024 artfynd.xlsx
+++ b/artfynd/A 29272-2024 artfynd.xlsx
@@ -1093,7 +1093,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122040064</v>
+        <v>122040082</v>
       </c>
       <c r="B6" t="n">
         <v>79727</v>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>564903</v>
+        <v>564751</v>
       </c>
       <c r="R6" t="n">
-        <v>6991894</v>
+        <v>6991849</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1195,7 +1195,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122040073</v>
+        <v>122040069</v>
       </c>
       <c r="B7" t="n">
         <v>79727</v>
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>564799</v>
+        <v>564823</v>
       </c>
       <c r="R7" t="n">
-        <v>6991861</v>
+        <v>6991869</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1297,7 +1297,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122040069</v>
+        <v>122040064</v>
       </c>
       <c r="B8" t="n">
         <v>79727</v>
@@ -1337,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>564823</v>
+        <v>564903</v>
       </c>
       <c r="R8" t="n">
-        <v>6991869</v>
+        <v>6991894</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1399,7 +1399,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122040082</v>
+        <v>122040073</v>
       </c>
       <c r="B9" t="n">
         <v>79727</v>
@@ -1439,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>564751</v>
+        <v>564799</v>
       </c>
       <c r="R9" t="n">
-        <v>6991849</v>
+        <v>6991861</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1501,10 +1501,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122040097</v>
+        <v>122040079</v>
       </c>
       <c r="B10" t="n">
-        <v>97139</v>
+        <v>79727</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1513,25 +1513,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1541,10 +1541,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>564799</v>
+        <v>564859</v>
       </c>
       <c r="R10" t="n">
-        <v>6991861</v>
+        <v>6991885</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1603,10 +1603,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122040079</v>
+        <v>122040097</v>
       </c>
       <c r="B11" t="n">
-        <v>79727</v>
+        <v>97139</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1615,25 +1615,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1643,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>564859</v>
+        <v>564799</v>
       </c>
       <c r="R11" t="n">
-        <v>6991885</v>
+        <v>6991861</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>

--- a/artfynd/A 29272-2024 artfynd.xlsx
+++ b/artfynd/A 29272-2024 artfynd.xlsx
@@ -1093,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122040082</v>
+        <v>122040064</v>
       </c>
       <c r="B6" t="n">
-        <v>79727</v>
+        <v>79732</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>564751</v>
+        <v>564903</v>
       </c>
       <c r="R6" t="n">
-        <v>6991849</v>
+        <v>6991894</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1195,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122040069</v>
+        <v>122040097</v>
       </c>
       <c r="B7" t="n">
-        <v>79727</v>
+        <v>97151</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1207,25 +1207,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>564823</v>
+        <v>564799</v>
       </c>
       <c r="R7" t="n">
-        <v>6991869</v>
+        <v>6991861</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1297,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122040064</v>
+        <v>122040073</v>
       </c>
       <c r="B8" t="n">
-        <v>79727</v>
+        <v>79732</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1337,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>564903</v>
+        <v>564799</v>
       </c>
       <c r="R8" t="n">
-        <v>6991894</v>
+        <v>6991861</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1399,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122040073</v>
+        <v>122040082</v>
       </c>
       <c r="B9" t="n">
-        <v>79727</v>
+        <v>79732</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1439,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>564799</v>
+        <v>564751</v>
       </c>
       <c r="R9" t="n">
-        <v>6991861</v>
+        <v>6991849</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1504,7 +1504,7 @@
         <v>122040079</v>
       </c>
       <c r="B10" t="n">
-        <v>79727</v>
+        <v>79732</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1603,10 +1603,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122040097</v>
+        <v>122040069</v>
       </c>
       <c r="B11" t="n">
-        <v>97139</v>
+        <v>79732</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1615,25 +1615,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1643,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>564799</v>
+        <v>564823</v>
       </c>
       <c r="R11" t="n">
-        <v>6991861</v>
+        <v>6991869</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>

--- a/artfynd/A 29272-2024 artfynd.xlsx
+++ b/artfynd/A 29272-2024 artfynd.xlsx
@@ -1093,7 +1093,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122040064</v>
+        <v>122040069</v>
       </c>
       <c r="B6" t="n">
         <v>79732</v>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>564903</v>
+        <v>564823</v>
       </c>
       <c r="R6" t="n">
-        <v>6991894</v>
+        <v>6991869</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1195,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122040097</v>
+        <v>122040073</v>
       </c>
       <c r="B7" t="n">
-        <v>97151</v>
+        <v>79732</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1207,25 +1207,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1297,7 +1297,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122040073</v>
+        <v>122040082</v>
       </c>
       <c r="B8" t="n">
         <v>79732</v>
@@ -1337,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>564799</v>
+        <v>564751</v>
       </c>
       <c r="R8" t="n">
-        <v>6991861</v>
+        <v>6991849</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1399,7 +1399,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122040082</v>
+        <v>122040079</v>
       </c>
       <c r="B9" t="n">
         <v>79732</v>
@@ -1439,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>564751</v>
+        <v>564859</v>
       </c>
       <c r="R9" t="n">
-        <v>6991849</v>
+        <v>6991885</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1501,10 +1501,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122040079</v>
+        <v>122040097</v>
       </c>
       <c r="B10" t="n">
-        <v>79732</v>
+        <v>97156</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1513,25 +1513,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1541,10 +1541,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>564859</v>
+        <v>564799</v>
       </c>
       <c r="R10" t="n">
-        <v>6991885</v>
+        <v>6991861</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1603,7 +1603,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122040069</v>
+        <v>122040064</v>
       </c>
       <c r="B11" t="n">
         <v>79732</v>
@@ -1643,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>564823</v>
+        <v>564903</v>
       </c>
       <c r="R11" t="n">
-        <v>6991869</v>
+        <v>6991894</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>

--- a/artfynd/A 29272-2024 artfynd.xlsx
+++ b/artfynd/A 29272-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1703,6 +1703,118 @@
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>124174736</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57491</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Stortjärndalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>564799</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6991861</v>
+      </c>
+      <c r="S12" t="n">
+        <v>50</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-04-17</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-04-17</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29272-2024 artfynd.xlsx
+++ b/artfynd/A 29272-2024 artfynd.xlsx
@@ -1712,7 +1712,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">

--- a/artfynd/A 29272-2024 artfynd.xlsx
+++ b/artfynd/A 29272-2024 artfynd.xlsx
@@ -1708,7 +1708,7 @@
         <v>124174736</v>
       </c>
       <c r="B12" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 29272-2024 artfynd.xlsx
+++ b/artfynd/A 29272-2024 artfynd.xlsx
@@ -1710,11 +1710,6 @@
       <c r="B12" t="n">
         <v>57635</v>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
-      </c>
       <c r="D12" t="inlineStr">
         <is>
           <t>NT</t>

--- a/artfynd/A 29272-2024 artfynd.xlsx
+++ b/artfynd/A 29272-2024 artfynd.xlsx
@@ -869,7 +869,7 @@
         <v>0</v>
       </c>
       <c r="AE3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG3" t="b">
         <v>0</v>

--- a/artfynd/A 29272-2024 artfynd.xlsx
+++ b/artfynd/A 29272-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,16 +678,11 @@
         <v>121696840</v>
       </c>
       <c r="B2" t="n">
-        <v>78639</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -777,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121697871</v>
+        <v>121696849</v>
       </c>
       <c r="B3" t="n">
-        <v>57385</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -850,26 +840,16 @@
           <t>2024-12-20</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>11:50</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-12-20</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>11:50</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="b">
         <v>0</v>
@@ -889,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121696844</v>
+        <v>122040064</v>
       </c>
       <c r="B4" t="n">
-        <v>55971</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -905,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>206004</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>564728</v>
+        <v>564903</v>
       </c>
       <c r="R4" t="n">
-        <v>6991842</v>
+        <v>6991894</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -959,12 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-12-20</t>
+          <t>2025-01-10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-12-20</t>
+          <t>2025-01-10</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121696849</v>
+        <v>122040069</v>
       </c>
       <c r="B5" t="n">
-        <v>79720</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1031,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>564728</v>
+        <v>564823</v>
       </c>
       <c r="R5" t="n">
-        <v>6991842</v>
+        <v>6991869</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1061,12 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-12-20</t>
+          <t>2025-01-10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-12-20</t>
+          <t>2025-01-10</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122040069</v>
+        <v>122040073</v>
       </c>
       <c r="B6" t="n">
-        <v>79732</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1133,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>564823</v>
+        <v>564799</v>
       </c>
       <c r="R6" t="n">
-        <v>6991869</v>
+        <v>6991861</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1195,15 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122040073</v>
+        <v>122040079</v>
       </c>
       <c r="B7" t="n">
-        <v>79732</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1235,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>564799</v>
+        <v>564859</v>
       </c>
       <c r="R7" t="n">
-        <v>6991861</v>
+        <v>6991885</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1300,12 +1260,7 @@
         <v>122040082</v>
       </c>
       <c r="B8" t="n">
-        <v>79732</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1399,37 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122040079</v>
+        <v>121697871</v>
       </c>
       <c r="B9" t="n">
-        <v>79732</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1439,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>564859</v>
+        <v>564728</v>
       </c>
       <c r="R9" t="n">
-        <v>6991885</v>
+        <v>6991842</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1469,19 +1419,29 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-01-10</t>
+          <t>2024-12-20</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-01-10</t>
+          <t>2024-12-20</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG9" t="b">
         <v>0</v>
@@ -1501,40 +1461,40 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122040097</v>
+        <v>124174736</v>
       </c>
       <c r="B10" t="n">
-        <v>97156</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stortjärndalen, Jmt</t>
@@ -1571,12 +1531,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-01-10</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-01-10</t>
+          <t>2025-04-17</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1603,53 +1568,57 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122040064</v>
+        <v>127326073</v>
       </c>
       <c r="B11" t="n">
-        <v>79732</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Stortjärndalen, Jmt</t>
+          <t>Stortjärndalen, Jämtland, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>564903</v>
+        <v>564915</v>
       </c>
       <c r="R11" t="n">
-        <v>6991894</v>
+        <v>6991875</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1673,12 +1642,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-01-10</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-01-10</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1705,10 +1674,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124174736</v>
+        <v>121696844</v>
       </c>
       <c r="B12" t="n">
-        <v>57635</v>
+        <v>56522</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1716,39 +1685,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>206004</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Stortjärndalen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>564799</v>
+        <v>564728</v>
       </c>
       <c r="R12" t="n">
-        <v>6991861</v>
+        <v>6991842</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1775,17 +1739,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2024-12-20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>2024-12-20</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1809,6 +1768,103 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>122040097</v>
+      </c>
+      <c r="B13" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Stortjärndalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>564799</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6991861</v>
+      </c>
+      <c r="S13" t="n">
+        <v>50</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
